--- a/чек лист.xlsx
+++ b/чек лист.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LordDeStar\Desktop\ClownsProduction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ClownsProduction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8DB1B0-76DD-45B0-A5E1-CCBB02E6C0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91703E8D-2620-41B4-93A9-AE7149EE1489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6825" yWindow="2085" windowWidth="38700" windowHeight="18915" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="398" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>№ Тест-кейса</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>Отрицательно</t>
+  </si>
+  <si>
+    <t>Ориентация</t>
+  </si>
+  <si>
+    <t>Гетеро</t>
+  </si>
+  <si>
+    <t>Гомо</t>
+  </si>
+  <si>
+    <t>Значение</t>
   </si>
 </sst>
 </file>
@@ -204,7 +216,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -265,6 +277,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -605,6 +623,7 @@
     <col min="2" max="2" width="35.5703125" customWidth="1"/>
     <col min="3" max="3" width="22.140625" customWidth="1"/>
     <col min="4" max="4" width="59.28515625" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="4" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -620,6 +639,15 @@
       <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
@@ -633,6 +661,15 @@
       </c>
       <c r="D2" s="8" t="s">
         <v>8</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
